--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/504185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077554</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80913889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,6 +1179,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86640009</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1280,6 +1305,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125191341</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1401,6 +1431,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125191357</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1522,6 +1557,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125191450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1643,6 +1683,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192412</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1769,6 +1814,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130812</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1880,6 +1930,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845675</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1991,6 +2046,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845714</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2102,6 +2162,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845674</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2213,6 +2278,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845676</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2324,6 +2394,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845731</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2435,8 +2510,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845736</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>